--- a/docs/Extras/SD2_S26/Bill-of-Materials-and-Budget/QORVO_RADIO2_REV2_BOM.xlsx
+++ b/docs/Extras/SD2_S26/Bill-of-Materials-and-Budget/QORVO_RADIO2_REV2_BOM.xlsx
@@ -13,10 +13,10 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision">
   <authors>
-    <author>tc={38cadd20-3a77-4882-a9de-85b7f8f7fca9}</author>
+    <author>tc={800e7e74-7f7a-4835-a646-7189a3809bae}</author>
   </authors>
   <commentList>
-    <comment authorId="0" xr:uid="{38cadd20-3a77-4882-a9de-85b7f8f7fca9}" ref="G29">
+    <comment authorId="0" xr:uid="{800e7e74-7f7a-4835-a646-7189a3809bae}" ref="G29">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -746,7 +746,7 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
-  <x18tc:person displayName="Ethan Hartman" id="{6b49283d-d503-4e6f-9806-4da0c7575e5f}" providerId="google-sheets"/>
+  <x18tc:person displayName="Ethan Hartman" id="{f0f7cf64-9504-42c5-a9a4-7e226b35448e}" providerId="google-sheets"/>
 </x18tc:personList>
 </file>
 
@@ -966,7 +966,7 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <x18tc:ThreadedComments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <x18tc:threadedComment ref="G29" dT="2026-03-18T07:04:14.00" personId="{6b49283d-d503-4e6f-9806-4da0c7575e5f}" id="{38cadd20-3a77-4882-a9de-85b7f8f7fca9}" done="0">
+  <x18tc:threadedComment ref="G29" dT="2026-03-18T07:04:14.00" personId="{f0f7cf64-9504-42c5-a9a4-7e226b35448e}" id="{800e7e74-7f7a-4835-a646-7189a3809bae}" done="0">
     <x18tc:text xml:space="preserve">No link, maybe https://www.digikey.com/en/products/detail/yageo/RC0402FR-071KL/726513</x18tc:text>
     <x18tc:extLst>
       <ext uri="{F7C98A9C-CBB3-438F-8F68-D28B6AF4A901}">
